--- a/data/trans_dic/P25C_R2_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P25C_R2_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos)</t>
+          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos) (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -622,12 +622,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,8</t>
+          <t>0,0; 19,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,29</t>
+          <t>0,0; 12,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,36</t>
+          <t>0,0; 5,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,33</t>
+          <t>0,0; 6,41</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 9,58</t>
+          <t>1,71; 9,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 3,51</t>
+          <t>0,11; 3,22</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,06</t>
+          <t>0,49; 5,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,06; 8,76</t>
+          <t>1,49; 8,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 5,26</t>
+          <t>1,55; 5,47</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,5</t>
+          <t>1,15; 5,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,14; 15,08</t>
+          <t>2,35; 14,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,01; 5,99</t>
+          <t>2,05; 6,35</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 8,28</t>
+          <t>1,55; 7,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,27</t>
+          <t>0,0; 15,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,6</t>
+          <t>1,65; 7,22</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,84</t>
+          <t>0,64; 2,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,87</t>
+          <t>2,36; 5,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,32</t>
+          <t>1,12; 3,33</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos)</t>
+          <t>Población que dejo de fumar con ayuda de su Centro de Salud (parches, pastillas, charlas, cursos) (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3403</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2654</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3071</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2302</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5131</t>
+          <t>0; 6072</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5848</t>
+          <t>0; 5846</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5528</t>
+          <t>0; 5508</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3320</t>
+          <t>0; 3008</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 7119</t>
+          <t>0; 6233</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6966</t>
+          <t>0; 6770</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1658; 8342</t>
+          <t>1491; 7976</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>740; 15229</t>
+          <t>466; 14001</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>958; 7933</t>
+          <t>772; 8296</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1772; 7555</t>
+          <t>1282; 7425</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3542; 12778</t>
+          <t>3758; 13296</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1750; 8552</t>
+          <t>1786; 8350</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1425; 6848</t>
+          <t>1069; 6540</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4030; 12040</t>
+          <t>4112; 12756</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1848; 9671</t>
+          <t>1811; 8345</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2523</t>
+          <t>0; 2815</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2119; 8877</t>
+          <t>2215; 9710</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4998; 24125</t>
+          <t>5471; 23595</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8274; 19798</t>
+          <t>7949; 19165</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>13092; 39386</t>
+          <t>13243; 39568</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C_R2_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P25C_R2_2023-Edad-trans_dic.xlsx
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,88</t>
+          <t>0,0; 19,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,42</t>
+          <t>0,0; 9,57</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,25</t>
+          <t>0,0; 12,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,76</t>
+          <t>0,0; 5,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,41</t>
+          <t>0,0; 5,37</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 4,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 9,16</t>
+          <t>2,22; 9,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 3,22</t>
+          <t>1,38; 5,29</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,29</t>
+          <t>0,62; 5,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 8,61</t>
+          <t>1,97; 8,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 5,47</t>
+          <t>1,44; 5,18</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,37</t>
+          <t>1,1; 5,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,35; 14,4</t>
+          <t>3,38; 14,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,35</t>
+          <t>2,03; 6,24</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,55; 7,15</t>
+          <t>1,41; 7,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,92</t>
+          <t>0,0; 16,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,65; 7,22</t>
+          <t>1,56; 6,84</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,78</t>
+          <t>1,4; 3,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,68</t>
+          <t>2,51; 5,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,33</t>
+          <t>2,11; 3,91</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1081</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6072</t>
+          <t>0; 6516</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5846</t>
+          <t>0; 5723</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>661</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1798</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5508</t>
+          <t>0; 5932</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3008</t>
+          <t>0; 3367</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6233</t>
+          <t>0; 5676</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>926</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>4712</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>5638</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6770</t>
+          <t>0; 4844</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1491; 7976</t>
+          <t>2057; 9209</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>466; 14001</t>
+          <t>2844; 10894</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>4048</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>7610</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>772; 8296</t>
+          <t>1028; 9320</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1282; 7425</t>
+          <t>1856; 8106</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3758; 13296</t>
+          <t>3746; 13427</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>4505</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>8029</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1786; 8350</t>
+          <t>1889; 9449</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1069; 6540</t>
+          <t>1643; 7271</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4112; 12756</t>
+          <t>4465; 13743</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>504</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>5304</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1811; 8345</t>
+          <t>1811; 9435</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2815</t>
+          <t>0; 3144</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2215; 9710</t>
+          <t>2310; 10148</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>14163</t>
+          <t>14930</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>13223</t>
+          <t>14531</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>27386</t>
+          <t>29461</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5471; 23595</t>
+          <t>9227; 23473</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>7949; 19165</t>
+          <t>9192; 21380</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>13243; 39568</t>
+          <t>21661; 40124</t>
         </is>
       </c>
     </row>
